--- a/data/ct_scoop/ct_scoop_links_2026-05-11.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-05-11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,52 +440,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PUTNAM SCOOP: New Candle Shop coming soon to Putnam</t>
+          <t>STORRS SCOOP: Monmouth Trading Cards coming soon to Storrs Center</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-windham-county-posts/putnam-scoop-new-candle-shop-coming-soon-to-putnam</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/storrs-scoop-monmouth-trading-cards-coming-soon-to-storrs-center</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MANCHESTER SCOOP: Nothing Bundt Cakes planning Manchester location!</t>
+          <t>WATERBURY SCOOP: Soft Serve Factory replaces Carvel in Waterbury!</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-nothing-bundt-cakes-planning-manchester-location</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/waterbury-scoop-soft-serve-factory-replaces-carvel-in-waterbury</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WEST HARTFORD SCOOP: Frisbie's Dairy Barn officially opens in WeHa!</t>
+          <t>FOXWOODS SCOOP: Hell's Kitchen back for 2 more seasons!</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-frisbies-dairy-barn-officially-opens-in-weha</t>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-hells-kitchen-back-for-2-more-seasons</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CANTON SCOOP: The Frosted Sheep Bake Shop opens in Canton</t>
+          <t>PUTNAM SCOOP: New Candle Shop coming soon to Putnam</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -493,14 +493,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/canton-scoop-the-frosted-sheep-bake-shop-opens-in-canton</t>
+          <t>https://www.theconnecticutscoop.com/all-windham-county-posts/putnam-scoop-new-candle-shop-coming-soon-to-putnam</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRANFORD SCOOP: O'Reilly Auto Parts eyeing Branford location</t>
+          <t>MANCHESTER SCOOP: Nothing Bundt Cakes planning Manchester location!</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -508,14 +508,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/branford-scoop-oreilly-auto-parts-eyeing-branford-location</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-nothing-bundt-cakes-planning-manchester-location</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MERIDEN SCOOP: Don Cola'o Panaderia opens in Meriden</t>
+          <t>WEST HARTFORD SCOOP: Frisbie's Dairy Barn officially opens in WeHa!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -523,14 +523,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-don-colao-panaderia-opens-in-meriden</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-frisbies-dairy-barn-officially-opens-in-weha</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EAST LYME SCOOP: Mystic Market sets opening date!</t>
+          <t>CANTON SCOOP: The Frosted Sheep Bake Shop opens in Canton</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -538,14 +538,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/east-lyme-scoop-mystic-market-sets-opening-date</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/canton-scoop-the-frosted-sheep-bake-shop-opens-in-canton</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FOXWOODS SCOOP: New tenants are popping up at Tanger Outlets</t>
+          <t>BRANFORD SCOOP: O'Reilly Auto Parts eyeing Branford location</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -553,20 +553,65 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-new-tenants-are-popping-up-at-tanger-outlets</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/branford-scoop-oreilly-auto-parts-eyeing-branford-location</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>MERIDEN SCOOP: Don Cola'o Panaderia opens in Meriden</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-don-colao-panaderia-opens-in-meriden</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EAST LYME SCOOP: Mystic Market sets opening date!</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/east-lyme-scoop-mystic-market-sets-opening-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FOXWOODS SCOOP: New tenants are popping up at Tanger Outlets</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/foxwoods-scoop-new-tenants-are-popping-up-at-tanger-outlets</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>MOHEGAN SUN SCOOP: Take a look at the new Bobby's Burgers!</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B13" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/mohegan-sun-scoop-take-a-look-at-the-new-bobbys-burgers</t>
         </is>
